--- a/docs/ia-bi/f3-fixtures-verite.xlsx
+++ b/docs/ia-bi/f3-fixtures-verite.xlsx
@@ -5,21 +5,21 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projet\epos-pfe\docs\ia-bi\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C04234E-85F9-4BE0-B732-EFC6CFFE0C3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF0BADC8-7C0D-4DFC-B52C-56E0974CEC49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Bareme" sheetId="1" r:id="rId1"/>
-    <sheet name="Donnees" sheetId="2" r:id="rId2"/>
-    <sheet name="Contributions" sheetId="3" r:id="rId3"/>
-    <sheet name="Difficulte" sheetId="4" r:id="rId4"/>
-    <sheet name="Discrimination" sheetId="5" r:id="rId5"/>
-    <sheet name="AlphaCronbach" sheetId="6" r:id="rId6"/>
-    <sheet name="Synthese" sheetId="7" r:id="rId7"/>
+    <sheet name="Vue-Synthese" sheetId="1" r:id="rId1"/>
+    <sheet name="Bareme" sheetId="2" r:id="rId2"/>
+    <sheet name="Donnees" sheetId="3" r:id="rId3"/>
+    <sheet name="Contributions" sheetId="4" r:id="rId4"/>
+    <sheet name="Difficulte" sheetId="5" r:id="rId5"/>
+    <sheet name="Discrimination" sheetId="6" r:id="rId6"/>
+    <sheet name="AlphaCronbach" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -43,7 +43,93 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="92">
+  <si>
+    <t>F3 — Fixture de Vérité (Ground Truth) — #358</t>
+  </si>
+  <si>
+    <t>DONNÉES BRUTES (v)</t>
+  </si>
+  <si>
+    <t>CONTRIBUTIONS (w)</t>
+  </si>
+  <si>
+    <t>FINAL</t>
+  </si>
+  <si>
+    <t>Étudiant</t>
+  </si>
+  <si>
+    <t>C1
+Binaire</t>
+  </si>
+  <si>
+    <t>C2
+Num.</t>
+  </si>
+  <si>
+    <t>C3
+Binaire</t>
+  </si>
+  <si>
+    <t>C4
+Num.</t>
+  </si>
+  <si>
+    <t>C1
+v × 4</t>
+  </si>
+  <si>
+    <t>C2
+v</t>
+  </si>
+  <si>
+    <t>C3
+v × 2</t>
+  </si>
+  <si>
+    <t>C4
+v</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>MOYENNE</t>
+  </si>
+  <si>
+    <t>Calculs de fiabilité (ddof=1) — voir feuilles Difficulte / Discrimination / AlphaCronbach</t>
+  </si>
+  <si>
+    <t>DIFFICULTÉ (p)</t>
+  </si>
+  <si>
+    <t>ALPHA DE CRONBACH</t>
+  </si>
+  <si>
+    <t>DISCRI. (r)</t>
+  </si>
+  <si>
+    <t>r = CORREL( contribution_item ; total − contribution_item )</t>
+  </si>
+  <si>
+    <t>Note méthodologique (contrat #358, app/stats/engine.py)</t>
+  </si>
+  <si>
+    <t>1)  Variances ÉCHANTILLON (ddof = 1) : au tableur, VAR.S() — jamais VAR.P(). C'est la formule utilisée dans la feuille AlphaCronbach.</t>
+  </si>
+  <si>
+    <t>2)  contribution(item) = valeur × pondération si le critère est BINAIRE ; valeur brute si NUMÉRIQUE. C'est l'arithmétique exacte de ExamItemSnapshot.weigh côté scoring — la pondération d'un critère NUMÉRIQUE plafonne, elle ne multiplie pas.</t>
+  </si>
+  <si>
+    <t>3)  8 étudiants seulement : ce jeu vérifie les FORMULES du moteur (engine.py), pas le contrat de refus « effectif insuffisant » — celui-ci a ses propres tests (test_engine_*.py) qui exercent les seuils de production (n≥10, n≥15…).</t>
+  </si>
+  <si>
+    <t>4)  Chaque cellule ci-dessus est une FORMULE (AVERAGE, CORREL, VAR.S) qui pointe vers les feuilles Donnees / Contributions / Difficulte / Discrimination / AlphaCronbach : aucune valeur n'est saisie à la main dans ce tableau de synthèse — il se recalcule si les données brutes changent.</t>
+  </si>
+  <si>
+    <t>5)  Le fixture JSON consommé par tests/test_fixtures_f3.py (ai-service/tests/fixtures/f3/) reprend VERBATIM les 9 valeurs de ce classeur (4 p, 4 r, 1 α), tolérance ±0.005.</t>
+  </si>
   <si>
     <t>F3 — Fixtures de vérité (#358) — barème des 4 critères</t>
   </si>
@@ -241,28 +327,17 @@
   </si>
   <si>
     <t>alpha de Cronbach</t>
-  </si>
-  <si>
-    <t>Synthèse — valeurs attendues (recopiées dans le fixture JSON, #358)</t>
-  </si>
-  <si>
-    <t>Difficulté p par critère</t>
-  </si>
-  <si>
-    <t>Discrimination r par critère</t>
-  </si>
-  <si>
-    <t>r</t>
-  </si>
-  <si>
-    <t>Alpha de Cronbach (k=4)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+  </numFmts>
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -272,7 +347,70 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="14"/>
+      <color rgb="FF1E293B"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF2563EB"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFD97706"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF1F5E3A"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF475569"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1F5E3A"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF334155"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1E293B"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF334155"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF64748B"/>
       <name val="Arial"/>
       <charset val="1"/>
     </font>
@@ -280,6 +418,18 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9.5"/>
+      <color rgb="FF475569"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <name val="Arial"/>
       <charset val="1"/>
     </font>
@@ -309,7 +459,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -318,17 +468,122 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF1F5F9"/>
+        <bgColor rgb="FFEFF6FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFF6FF"/>
+        <bgColor rgb="FFF1F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFBEB"/>
+        <bgColor rgb="FFFAFDFB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0FDF4"/>
+        <bgColor rgb="FFF8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAFDFB"/>
+        <bgColor rgb="FFFCFCFD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCFCFD"/>
+        <bgColor rgb="FFFAFDFB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FAFC"/>
+        <bgColor rgb="FFFAFDFB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1F5E3A"/>
-        <bgColor rgb="FF008000"/>
+        <bgColor rgb="FF334155"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF1F5E3A"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFCBD5E1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE2E8F0"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE2E8F0"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF1F5E3A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE2E8F0"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -350,21 +605,93 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -382,7 +709,7 @@
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF1F5E3A"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
@@ -391,12 +718,12 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFFFFBEB"/>
+      <rgbColor rgb="FFF0FDF4"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FFCBD5E1"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -406,29 +733,29 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFEFF6FF"/>
+      <rgbColor rgb="FFE2E8F0"/>
+      <rgbColor rgb="FFFAFDFB"/>
+      <rgbColor rgb="FFF8FAFC"/>
+      <rgbColor rgb="FFFCFCFD"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FFF1F5F9"/>
+      <rgbColor rgb="FF2563EB"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FFD97706"/>
+      <rgbColor rgb="FF64748B"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF475569"/>
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF1F5E3A"/>
+      <rgbColor rgb="FF334155"/>
+      <rgbColor rgb="FF1E293B"/>
       <rgbColor rgb="00003366"/>
       <rgbColor rgb="00339966"/>
       <rgbColor rgb="00003300"/>
@@ -629,141 +956,758 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10" style="3" customWidth="1"/>
-    <col min="2" max="2" width="26" style="3" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="18.21875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="15.5546875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="89.109375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="18.5546875" customWidth="1"/>
+    <col min="2" max="3" width="9" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.21875" customWidth="1"/>
+    <col min="6" max="6" width="13.6640625" customWidth="1"/>
+    <col min="7" max="8" width="9" customWidth="1"/>
+    <col min="9" max="9" width="9.77734375" customWidth="1"/>
+    <col min="10" max="10" width="25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+    </row>
+    <row r="2" spans="1:10" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="34" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="str">
+        <f>Donnees!A4</f>
+        <v>E1</v>
+      </c>
+      <c r="B5" s="10">
+        <f>Donnees!B4</f>
+        <v>1</v>
+      </c>
+      <c r="C5" s="10">
+        <f>Donnees!C4</f>
+        <v>8</v>
+      </c>
+      <c r="D5" s="10">
+        <f>Donnees!D4</f>
+        <v>1</v>
+      </c>
+      <c r="E5" s="10">
+        <f>Donnees!E4</f>
+        <v>4</v>
+      </c>
+      <c r="F5" s="10">
+        <f>Contributions!B4</f>
+        <v>4</v>
+      </c>
+      <c r="G5" s="10">
+        <f>Contributions!C4</f>
+        <v>8</v>
+      </c>
+      <c r="H5" s="10">
+        <f>Contributions!D4</f>
+        <v>2</v>
+      </c>
+      <c r="I5" s="10">
+        <f>Contributions!E4</f>
+        <v>4</v>
+      </c>
+      <c r="J5" s="11">
+        <f>Contributions!F4</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="12" t="str">
+        <f>Donnees!A5</f>
+        <v>E2</v>
+      </c>
+      <c r="B6" s="13">
+        <f>Donnees!B5</f>
+        <v>1</v>
+      </c>
+      <c r="C6" s="13">
+        <f>Donnees!C5</f>
+        <v>6</v>
+      </c>
+      <c r="D6" s="13">
+        <f>Donnees!D5</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="13">
+        <f>Donnees!E5</f>
+        <v>2</v>
+      </c>
+      <c r="F6" s="13">
+        <f>Contributions!B5</f>
+        <v>4</v>
+      </c>
+      <c r="G6" s="13">
+        <f>Contributions!C5</f>
+        <v>6</v>
+      </c>
+      <c r="H6" s="13">
+        <f>Contributions!D5</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="13">
+        <f>Contributions!E5</f>
+        <v>2</v>
+      </c>
+      <c r="J6" s="11">
+        <f>Contributions!F5</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="str">
+        <f>Donnees!A6</f>
+        <v>E3</v>
+      </c>
+      <c r="B7" s="10">
+        <f>Donnees!B6</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="10">
+        <f>Donnees!C6</f>
+        <v>9</v>
+      </c>
+      <c r="D7" s="10">
+        <f>Donnees!D6</f>
+        <v>1</v>
+      </c>
+      <c r="E7" s="10">
+        <f>Donnees!E6</f>
+        <v>4</v>
+      </c>
+      <c r="F7" s="10">
+        <f>Contributions!B6</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="10">
+        <f>Contributions!C6</f>
+        <v>9</v>
+      </c>
+      <c r="H7" s="10">
+        <f>Contributions!D6</f>
+        <v>2</v>
+      </c>
+      <c r="I7" s="10">
+        <f>Contributions!E6</f>
+        <v>4</v>
+      </c>
+      <c r="J7" s="11">
+        <f>Contributions!F6</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="12" t="str">
+        <f>Donnees!A7</f>
+        <v>E4</v>
+      </c>
+      <c r="B8" s="13">
+        <f>Donnees!B7</f>
+        <v>1</v>
+      </c>
+      <c r="C8" s="13">
+        <f>Donnees!C7</f>
+        <v>5</v>
+      </c>
+      <c r="D8" s="13">
+        <f>Donnees!D7</f>
+        <v>1</v>
+      </c>
+      <c r="E8" s="13">
+        <f>Donnees!E7</f>
+        <v>2</v>
+      </c>
+      <c r="F8" s="13">
+        <f>Contributions!B7</f>
+        <v>4</v>
+      </c>
+      <c r="G8" s="13">
+        <f>Contributions!C7</f>
+        <v>5</v>
+      </c>
+      <c r="H8" s="13">
+        <f>Contributions!D7</f>
+        <v>2</v>
+      </c>
+      <c r="I8" s="13">
+        <f>Contributions!E7</f>
+        <v>2</v>
+      </c>
+      <c r="J8" s="11">
+        <f>Contributions!F7</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="9" t="str">
+        <f>Donnees!A8</f>
+        <v>E5</v>
+      </c>
+      <c r="B9" s="10">
+        <f>Donnees!B8</f>
+        <v>0</v>
+      </c>
+      <c r="C9" s="10">
+        <f>Donnees!C8</f>
+        <v>7</v>
+      </c>
+      <c r="D9" s="10">
+        <f>Donnees!D8</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="10">
+        <f>Donnees!E8</f>
+        <v>4</v>
+      </c>
+      <c r="F9" s="10">
+        <f>Contributions!B8</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="10">
+        <f>Contributions!C8</f>
+        <v>7</v>
+      </c>
+      <c r="H9" s="10">
+        <f>Contributions!D8</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="10">
+        <f>Contributions!E8</f>
+        <v>4</v>
+      </c>
+      <c r="J9" s="11">
+        <f>Contributions!F8</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="12" t="str">
+        <f>Donnees!A9</f>
+        <v>E6</v>
+      </c>
+      <c r="B10" s="13">
+        <f>Donnees!B9</f>
+        <v>1</v>
+      </c>
+      <c r="C10" s="13">
+        <f>Donnees!C9</f>
+        <v>4</v>
+      </c>
+      <c r="D10" s="13">
+        <f>Donnees!D9</f>
+        <v>1</v>
+      </c>
+      <c r="E10" s="13">
+        <f>Donnees!E9</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="13">
+        <f>Contributions!B9</f>
+        <v>4</v>
+      </c>
+      <c r="G10" s="13">
+        <f>Contributions!C9</f>
+        <v>4</v>
+      </c>
+      <c r="H10" s="13">
+        <f>Contributions!D9</f>
+        <v>2</v>
+      </c>
+      <c r="I10" s="13">
+        <f>Contributions!E9</f>
+        <v>0</v>
+      </c>
+      <c r="J10" s="11">
+        <f>Contributions!F9</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="9" t="str">
+        <f>Donnees!A10</f>
+        <v>E7</v>
+      </c>
+      <c r="B11" s="10">
+        <f>Donnees!B10</f>
+        <v>1</v>
+      </c>
+      <c r="C11" s="10">
+        <f>Donnees!C10</f>
+        <v>10</v>
+      </c>
+      <c r="D11" s="10">
+        <f>Donnees!D10</f>
+        <v>1</v>
+      </c>
+      <c r="E11" s="10">
+        <f>Donnees!E10</f>
+        <v>4</v>
+      </c>
+      <c r="F11" s="10">
+        <f>Contributions!B10</f>
+        <v>4</v>
+      </c>
+      <c r="G11" s="10">
+        <f>Contributions!C10</f>
+        <v>10</v>
+      </c>
+      <c r="H11" s="10">
+        <f>Contributions!D10</f>
+        <v>2</v>
+      </c>
+      <c r="I11" s="10">
+        <f>Contributions!E10</f>
+        <v>4</v>
+      </c>
+      <c r="J11" s="11">
+        <f>Contributions!F10</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="12" t="str">
+        <f>Donnees!A11</f>
+        <v>E8</v>
+      </c>
+      <c r="B12" s="13">
+        <f>Donnees!B11</f>
+        <v>0</v>
+      </c>
+      <c r="C12" s="13">
+        <f>Donnees!C11</f>
+        <v>3</v>
+      </c>
+      <c r="D12" s="13">
+        <f>Donnees!D11</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="13">
+        <f>Donnees!E11</f>
+        <v>2</v>
+      </c>
+      <c r="F12" s="13">
+        <f>Contributions!B11</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="13">
+        <f>Contributions!C11</f>
+        <v>3</v>
+      </c>
+      <c r="H12" s="13">
+        <f>Contributions!D11</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="13">
+        <f>Contributions!E11</f>
+        <v>2</v>
+      </c>
+      <c r="J12" s="11">
+        <f>Contributions!F11</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="15">
+        <f>AVERAGE(B5:B12)</f>
+        <v>0.625</v>
+      </c>
+      <c r="C13" s="15">
+        <f>AVERAGE(C5:C12)</f>
+        <v>6.5</v>
+      </c>
+      <c r="D13" s="15">
+        <f>AVERAGE(D5:D12)</f>
+        <v>0.625</v>
+      </c>
+      <c r="E13" s="15">
+        <f>AVERAGE(E5:E12)</f>
+        <v>2.75</v>
+      </c>
+      <c r="F13" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="30"/>
+      <c r="H13" s="30"/>
+      <c r="I13" s="30"/>
+      <c r="J13" s="30"/>
+    </row>
+    <row r="14" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="17">
+        <f>Difficulte!E4</f>
+        <v>0.625</v>
+      </c>
+      <c r="C14" s="17">
+        <f>Difficulte!E5</f>
+        <v>0.65</v>
+      </c>
+      <c r="D14" s="17">
+        <f>Difficulte!E6</f>
+        <v>0.625</v>
+      </c>
+      <c r="E14" s="17">
+        <f>Difficulte!E7</f>
+        <v>0.6875</v>
+      </c>
+      <c r="F14" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" s="35"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="35"/>
+      <c r="J14" s="18">
+        <f>AlphaCronbach!B12</f>
+        <v>0.5213675213675214</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="20">
+        <f>Discrimination!D4</f>
+        <v>3.3058980245364314E-2</v>
+      </c>
+      <c r="C15" s="20">
+        <f>Discrimination!D5</f>
+        <v>0.62994078834871203</v>
+      </c>
+      <c r="D15" s="20">
+        <f>Discrimination!D6</f>
+        <v>0.48434343544519759</v>
+      </c>
+      <c r="E15" s="20">
+        <f>Discrimination!D7</f>
+        <v>0.34879055774945689</v>
+      </c>
+      <c r="F15" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="G15" s="30"/>
+      <c r="H15" s="30"/>
+      <c r="I15" s="30"/>
+      <c r="J15" s="30"/>
+    </row>
+    <row r="17" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="31"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="31"/>
+    </row>
+    <row r="18" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="29"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="29"/>
+      <c r="H18" s="29"/>
+      <c r="I18" s="29"/>
+      <c r="J18" s="29"/>
+    </row>
+    <row r="19" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="29"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="29"/>
+      <c r="I19" s="29"/>
+      <c r="J19" s="29"/>
+    </row>
+    <row r="20" spans="1:10" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="29"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="29"/>
+      <c r="I20" s="29"/>
+      <c r="J20" s="29"/>
+    </row>
+    <row r="21" spans="1:10" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" s="29"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="29"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="29"/>
+      <c r="G21" s="29"/>
+      <c r="H21" s="29"/>
+      <c r="I21" s="29"/>
+      <c r="J21" s="29"/>
+    </row>
+    <row r="22" spans="1:10" ht="43.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="29"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="29"/>
+      <c r="H22" s="29"/>
+      <c r="I22" s="29"/>
+      <c r="J22" s="29"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="F14:I14"/>
+    <mergeCell ref="A21:J21"/>
+    <mergeCell ref="A22:J22"/>
+    <mergeCell ref="F15:J15"/>
+    <mergeCell ref="A17:J17"/>
+    <mergeCell ref="A18:J18"/>
+    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="A20:J20"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.109375" style="21" customWidth="1"/>
+    <col min="2" max="2" width="26" style="21" customWidth="1"/>
+    <col min="3" max="3" width="12" style="21" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="16.21875" style="21" customWidth="1"/>
+    <col min="6" max="6" width="85.88671875" style="21" customWidth="1"/>
+    <col min="10" max="10" width="36.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+      <c r="A1" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="22" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="23">
         <v>1</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="B4" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="23">
+        <v>4</v>
+      </c>
+      <c r="E4" s="23"/>
+      <c r="F4" s="24" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="23">
+        <v>2</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="23">
+        <v>10</v>
+      </c>
+      <c r="E5" s="23">
+        <v>10</v>
+      </c>
+      <c r="F5" s="24" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="23">
         <v>3</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="5">
-        <v>1</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="5">
-        <v>4</v>
-      </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="5">
-        <v>2</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="5">
-        <v>10</v>
-      </c>
-      <c r="E5" s="5">
-        <v>10</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="5">
-        <v>3</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="5">
-        <v>2</v>
-      </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="6" t="s">
-        <v>9</v>
+      <c r="B6" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="23">
+        <v>2</v>
+      </c>
+      <c r="E6" s="23"/>
+      <c r="F6" s="24" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="5">
-        <v>4</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="5">
-        <v>4</v>
-      </c>
-      <c r="E7" s="5">
-        <v>4</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>15</v>
+      <c r="A7" s="23">
+        <v>4</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="23">
+        <v>4</v>
+      </c>
+      <c r="E7" s="23">
+        <v>4</v>
+      </c>
+      <c r="F7" s="24" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
-        <v>16</v>
+      <c r="A9" s="25" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
-        <v>17</v>
+      <c r="A10" s="21" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
-        <v>18</v>
+      <c r="A11" s="21" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
-        <v>19</v>
+      <c r="A12" s="21" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="27" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="1:1" ht="28.8" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:1" ht="38.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:1" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="1:1" ht="43.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="21" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -775,177 +1719,177 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10" style="3" customWidth="1"/>
-    <col min="2" max="2" width="15" style="3" customWidth="1"/>
-    <col min="3" max="3" width="20" style="3" customWidth="1"/>
-    <col min="4" max="4" width="15" style="3" customWidth="1"/>
-    <col min="5" max="5" width="20" style="3" customWidth="1"/>
+    <col min="1" max="1" width="10" style="21" customWidth="1"/>
+    <col min="2" max="2" width="15" style="21" customWidth="1"/>
+    <col min="3" max="3" width="20" style="21" customWidth="1"/>
+    <col min="4" max="4" width="15" style="21" customWidth="1"/>
+    <col min="5" max="5" width="20" style="21" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
+      <c r="A1" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>25</v>
+      <c r="A3" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" s="5">
+      <c r="A4" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="23">
         <v>1</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="23">
         <v>8</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="23">
         <v>1</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="23">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="5">
+      <c r="A5" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="23">
         <v>1</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="23">
         <v>6</v>
       </c>
-      <c r="D5" s="5">
-        <v>0</v>
-      </c>
-      <c r="E5" s="5">
+      <c r="D5" s="23">
+        <v>0</v>
+      </c>
+      <c r="E5" s="23">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="5">
-        <v>0</v>
-      </c>
-      <c r="C6" s="5">
+      <c r="A6" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" s="23">
+        <v>0</v>
+      </c>
+      <c r="C6" s="23">
         <v>9</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="23">
         <v>1</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="23">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="5">
+      <c r="A7" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="23">
         <v>1</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="23">
         <v>5</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="23">
         <v>1</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="23">
         <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="5">
-        <v>0</v>
-      </c>
-      <c r="C8" s="5">
+      <c r="A8" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="23">
+        <v>0</v>
+      </c>
+      <c r="C8" s="23">
         <v>7</v>
       </c>
-      <c r="D8" s="5">
-        <v>0</v>
-      </c>
-      <c r="E8" s="5">
+      <c r="D8" s="23">
+        <v>0</v>
+      </c>
+      <c r="E8" s="23">
         <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" s="5">
+      <c r="A9" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" s="23">
         <v>1</v>
       </c>
-      <c r="C9" s="5">
-        <v>4</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="23">
+        <v>4</v>
+      </c>
+      <c r="D9" s="23">
         <v>1</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="23">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" s="5">
+      <c r="A10" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" s="23">
         <v>1</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="23">
         <v>10</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="23">
         <v>1</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="23">
         <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="5">
-        <v>0</v>
-      </c>
-      <c r="C11" s="5">
+      <c r="A11" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" s="23">
+        <v>0</v>
+      </c>
+      <c r="C11" s="23">
         <v>3</v>
       </c>
-      <c r="D11" s="5">
-        <v>0</v>
-      </c>
-      <c r="E11" s="5">
+      <c r="D11" s="23">
+        <v>0</v>
+      </c>
+      <c r="E11" s="23">
         <v>2</v>
       </c>
     </row>
@@ -958,250 +1902,250 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10" style="3" customWidth="1"/>
-    <col min="2" max="5" width="13" style="3" customWidth="1"/>
-    <col min="6" max="6" width="41" style="3" customWidth="1"/>
+    <col min="1" max="1" width="10" style="21" customWidth="1"/>
+    <col min="2" max="5" width="13" style="21" customWidth="1"/>
+    <col min="6" max="6" width="39.77734375" style="21" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="A1" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>39</v>
+      <c r="A3" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="F3" s="22" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="str">
+      <c r="A4" s="24" t="str">
         <f>Donnees!A4</f>
         <v>E1</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="26">
         <f>IF(Bareme!$C$4="BINAIRE",Donnees!B4*Bareme!$D$4,Donnees!B4)</f>
         <v>4</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="26">
         <f>IF(Bareme!$C$5="BINAIRE",Donnees!C4*Bareme!$D$5,Donnees!C4)</f>
         <v>8</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="26">
         <f>IF(Bareme!$C$6="BINAIRE",Donnees!D4*Bareme!$D$6,Donnees!D4)</f>
         <v>2</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="26">
         <f>IF(Bareme!$C$7="BINAIRE",Donnees!E4*Bareme!$D$7,Donnees!E4)</f>
         <v>4</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="26">
         <f t="shared" ref="F4:F11" si="0">SUM(B4:E4)</f>
         <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="str">
+      <c r="A5" s="24" t="str">
         <f>Donnees!A5</f>
         <v>E2</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="26">
         <f>IF(Bareme!$C$4="BINAIRE",Donnees!B5*Bareme!$D$4,Donnees!B5)</f>
         <v>4</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="26">
         <f>IF(Bareme!$C$5="BINAIRE",Donnees!C5*Bareme!$D$5,Donnees!C5)</f>
         <v>6</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="26">
         <f>IF(Bareme!$C$6="BINAIRE",Donnees!D5*Bareme!$D$6,Donnees!D5)</f>
         <v>0</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="26">
         <f>IF(Bareme!$C$7="BINAIRE",Donnees!E5*Bareme!$D$7,Donnees!E5)</f>
         <v>2</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="26">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="str">
+      <c r="A6" s="24" t="str">
         <f>Donnees!A6</f>
         <v>E3</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="26">
         <f>IF(Bareme!$C$4="BINAIRE",Donnees!B6*Bareme!$D$4,Donnees!B6)</f>
         <v>0</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="26">
         <f>IF(Bareme!$C$5="BINAIRE",Donnees!C6*Bareme!$D$5,Donnees!C6)</f>
         <v>9</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="26">
         <f>IF(Bareme!$C$6="BINAIRE",Donnees!D6*Bareme!$D$6,Donnees!D6)</f>
         <v>2</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="26">
         <f>IF(Bareme!$C$7="BINAIRE",Donnees!E6*Bareme!$D$7,Donnees!E6)</f>
         <v>4</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="26">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="str">
+      <c r="A7" s="24" t="str">
         <f>Donnees!A7</f>
         <v>E4</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="26">
         <f>IF(Bareme!$C$4="BINAIRE",Donnees!B7*Bareme!$D$4,Donnees!B7)</f>
         <v>4</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="26">
         <f>IF(Bareme!$C$5="BINAIRE",Donnees!C7*Bareme!$D$5,Donnees!C7)</f>
         <v>5</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="26">
         <f>IF(Bareme!$C$6="BINAIRE",Donnees!D7*Bareme!$D$6,Donnees!D7)</f>
         <v>2</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="26">
         <f>IF(Bareme!$C$7="BINAIRE",Donnees!E7*Bareme!$D$7,Donnees!E7)</f>
         <v>2</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="26">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="str">
+      <c r="A8" s="24" t="str">
         <f>Donnees!A8</f>
         <v>E5</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="26">
         <f>IF(Bareme!$C$4="BINAIRE",Donnees!B8*Bareme!$D$4,Donnees!B8)</f>
         <v>0</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="26">
         <f>IF(Bareme!$C$5="BINAIRE",Donnees!C8*Bareme!$D$5,Donnees!C8)</f>
         <v>7</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="26">
         <f>IF(Bareme!$C$6="BINAIRE",Donnees!D8*Bareme!$D$6,Donnees!D8)</f>
         <v>0</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="26">
         <f>IF(Bareme!$C$7="BINAIRE",Donnees!E8*Bareme!$D$7,Donnees!E8)</f>
         <v>4</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="26">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="str">
+      <c r="A9" s="24" t="str">
         <f>Donnees!A9</f>
         <v>E6</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="26">
         <f>IF(Bareme!$C$4="BINAIRE",Donnees!B9*Bareme!$D$4,Donnees!B9)</f>
         <v>4</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="26">
         <f>IF(Bareme!$C$5="BINAIRE",Donnees!C9*Bareme!$D$5,Donnees!C9)</f>
         <v>4</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="26">
         <f>IF(Bareme!$C$6="BINAIRE",Donnees!D9*Bareme!$D$6,Donnees!D9)</f>
         <v>2</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="26">
         <f>IF(Bareme!$C$7="BINAIRE",Donnees!E9*Bareme!$D$7,Donnees!E9)</f>
         <v>0</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="26">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="str">
+      <c r="A10" s="24" t="str">
         <f>Donnees!A10</f>
         <v>E7</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="26">
         <f>IF(Bareme!$C$4="BINAIRE",Donnees!B10*Bareme!$D$4,Donnees!B10)</f>
         <v>4</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="26">
         <f>IF(Bareme!$C$5="BINAIRE",Donnees!C10*Bareme!$D$5,Donnees!C10)</f>
         <v>10</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="26">
         <f>IF(Bareme!$C$6="BINAIRE",Donnees!D10*Bareme!$D$6,Donnees!D10)</f>
         <v>2</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="26">
         <f>IF(Bareme!$C$7="BINAIRE",Donnees!E10*Bareme!$D$7,Donnees!E10)</f>
         <v>4</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="26">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="str">
+      <c r="A11" s="24" t="str">
         <f>Donnees!A11</f>
         <v>E8</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="26">
         <f>IF(Bareme!$C$4="BINAIRE",Donnees!B11*Bareme!$D$4,Donnees!B11)</f>
         <v>0</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="26">
         <f>IF(Bareme!$C$5="BINAIRE",Donnees!C11*Bareme!$D$5,Donnees!C11)</f>
         <v>3</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="26">
         <f>IF(Bareme!$C$6="BINAIRE",Donnees!D11*Bareme!$D$6,Donnees!D11)</f>
         <v>0</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="26">
         <f>IF(Bareme!$C$7="BINAIRE",Donnees!E11*Bareme!$D$7,Donnees!E11)</f>
         <v>2</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="26">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -1215,124 +2159,124 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10" style="3" customWidth="1"/>
-    <col min="2" max="2" width="18" style="3" customWidth="1"/>
-    <col min="3" max="3" width="15.77734375" style="3" customWidth="1"/>
-    <col min="4" max="4" width="20" style="3" customWidth="1"/>
-    <col min="5" max="5" width="27.21875" style="3" customWidth="1"/>
+    <col min="1" max="1" width="10" style="21" customWidth="1"/>
+    <col min="2" max="2" width="20.88671875" style="21" customWidth="1"/>
+    <col min="3" max="3" width="18.109375" style="21" customWidth="1"/>
+    <col min="4" max="4" width="23" style="21" customWidth="1"/>
+    <col min="5" max="5" width="19.77734375" style="21" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
+      <c r="A1" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="24">
         <v>1</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="6">
-        <v>1</v>
-      </c>
-      <c r="B4" s="8">
+      <c r="B4" s="26">
         <f>AVERAGE(Donnees!B4:B11)</f>
         <v>0.625</v>
       </c>
-      <c r="C4" s="8" t="str">
+      <c r="C4" s="26" t="str">
         <f>Bareme!C4</f>
         <v>BINAIRE</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="26">
         <f>IF(Bareme!C4="BINAIRE",1,Bareme!E4)</f>
         <v>1</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="26">
         <f>B4/D4</f>
         <v>0.625</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="6">
-        <v>2</v>
-      </c>
-      <c r="B5" s="8">
+      <c r="A5" s="24">
+        <v>2</v>
+      </c>
+      <c r="B5" s="26">
         <f>AVERAGE(Donnees!C4:C11)</f>
         <v>6.5</v>
       </c>
-      <c r="C5" s="8" t="str">
+      <c r="C5" s="26" t="str">
         <f>Bareme!C5</f>
         <v>NUMERIQUE</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="26">
         <f>IF(Bareme!C5="BINAIRE",1,Bareme!E5)</f>
         <v>10</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="26">
         <f>B5/D5</f>
         <v>0.65</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="6">
+      <c r="A6" s="24">
         <v>3</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="26">
         <f>AVERAGE(Donnees!D4:D11)</f>
         <v>0.625</v>
       </c>
-      <c r="C6" s="8" t="str">
+      <c r="C6" s="26" t="str">
         <f>Bareme!C6</f>
         <v>BINAIRE</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="26">
         <f>IF(Bareme!C6="BINAIRE",1,Bareme!E6)</f>
         <v>1</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="26">
         <f>B6/D6</f>
         <v>0.625</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="6">
-        <v>4</v>
-      </c>
-      <c r="B7" s="8">
+      <c r="A7" s="24">
+        <v>4</v>
+      </c>
+      <c r="B7" s="26">
         <f>AVERAGE(Donnees!E4:E11)</f>
         <v>2.75</v>
       </c>
-      <c r="C7" s="8" t="str">
+      <c r="C7" s="26" t="str">
         <f>Bareme!C7</f>
         <v>NUMERIQUE</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="26">
         <f>IF(Bareme!C7="BINAIRE",1,Bareme!E7)</f>
         <v>4</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="26">
         <f>B7/D7</f>
         <v>0.6875</v>
       </c>
@@ -1346,289 +2290,290 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10" style="3" customWidth="1"/>
-    <col min="2" max="3" width="26" style="3" customWidth="1"/>
-    <col min="4" max="4" width="12" style="3" customWidth="1"/>
+    <col min="1" max="1" width="10" style="21" customWidth="1"/>
+    <col min="2" max="3" width="26" style="21" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="A1" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="24">
         <v>1</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="6">
-        <v>1</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D4" s="8">
+      <c r="B4" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="D4" s="26">
         <f>CORREL(Contributions!B4:B11,B9:B16)</f>
         <v>3.3058980245364314E-2</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="6">
-        <v>2</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D5" s="8">
+      <c r="A5" s="24">
+        <v>2</v>
+      </c>
+      <c r="B5" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5" s="26">
         <f>CORREL(Contributions!C4:C11,C9:C16)</f>
         <v>0.62994078834871203</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="6">
+      <c r="A6" s="24">
         <v>3</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" s="8">
+      <c r="B6" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="D6" s="26">
         <f>CORREL(Contributions!D4:D11,D9:D16)</f>
         <v>0.48434343544519759</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="9">
-        <v>4</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="D7" s="8">
+      <c r="A7" s="27">
+        <v>4</v>
+      </c>
+      <c r="B7" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="D7" s="26">
         <f>CORREL(Contributions!E4:E11,E9:E16)</f>
         <v>0.34879055774945689</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>59</v>
+      <c r="A8" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="str">
+      <c r="A9" s="24" t="str">
         <f>Contributions!A4</f>
         <v>E1</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="26">
         <f>Contributions!$F$4-Contributions!B4</f>
         <v>14</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="26">
         <f>Contributions!$F$4-Contributions!C4</f>
         <v>10</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="26">
         <f>Contributions!$F$4-Contributions!D4</f>
         <v>16</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="26">
         <f>Contributions!$F$4-Contributions!E4</f>
         <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="str">
+      <c r="A10" s="24" t="str">
         <f>Contributions!A5</f>
         <v>E2</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="26">
         <f>Contributions!$F$5-Contributions!B5</f>
         <v>8</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="26">
         <f>Contributions!$F$5-Contributions!C5</f>
         <v>6</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="26">
         <f>Contributions!$F$5-Contributions!D5</f>
         <v>12</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="26">
         <f>Contributions!$F$5-Contributions!E5</f>
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="str">
+      <c r="A11" s="24" t="str">
         <f>Contributions!A6</f>
         <v>E3</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="26">
         <f>Contributions!$F$6-Contributions!B6</f>
         <v>15</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="26">
         <f>Contributions!$F$6-Contributions!C6</f>
         <v>6</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="26">
         <f>Contributions!$F$6-Contributions!D6</f>
         <v>13</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="26">
         <f>Contributions!$F$6-Contributions!E6</f>
         <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="6" t="str">
+      <c r="A12" s="24" t="str">
         <f>Contributions!A7</f>
         <v>E4</v>
       </c>
-      <c r="B12" s="8">
+      <c r="B12" s="26">
         <f>Contributions!$F$7-Contributions!B7</f>
         <v>9</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="26">
         <f>Contributions!$F$7-Contributions!C7</f>
         <v>8</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="26">
         <f>Contributions!$F$7-Contributions!D7</f>
         <v>11</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="26">
         <f>Contributions!$F$7-Contributions!E7</f>
         <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="6" t="str">
+      <c r="A13" s="24" t="str">
         <f>Contributions!A8</f>
         <v>E5</v>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="26">
         <f>Contributions!$F$8-Contributions!B8</f>
         <v>11</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="26">
         <f>Contributions!$F$8-Contributions!C8</f>
         <v>4</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="26">
         <f>Contributions!$F$8-Contributions!D8</f>
         <v>11</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="26">
         <f>Contributions!$F$8-Contributions!E8</f>
         <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="str">
+      <c r="A14" s="24" t="str">
         <f>Contributions!A9</f>
         <v>E6</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="26">
         <f>Contributions!$F$9-Contributions!B9</f>
         <v>6</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="26">
         <f>Contributions!$F$9-Contributions!C9</f>
         <v>6</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="26">
         <f>Contributions!$F$9-Contributions!D9</f>
         <v>8</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="26">
         <f>Contributions!$F$9-Contributions!E9</f>
         <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="6" t="str">
+      <c r="A15" s="24" t="str">
         <f>Contributions!A10</f>
         <v>E7</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="26">
         <f>Contributions!$F$10-Contributions!B10</f>
         <v>16</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="26">
         <f>Contributions!$F$10-Contributions!C10</f>
         <v>10</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="26">
         <f>Contributions!$F$10-Contributions!D10</f>
         <v>18</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="26">
         <f>Contributions!$F$10-Contributions!E10</f>
         <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="str">
+      <c r="A16" s="24" t="str">
         <f>Contributions!A11</f>
         <v>E8</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="26">
         <f>Contributions!$F$11-Contributions!B11</f>
         <v>5</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="26">
         <f>Contributions!$F$11-Contributions!C11</f>
         <v>2</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="26">
         <f>Contributions!$F$11-Contributions!D11</f>
         <v>5</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E16" s="26">
         <f>Contributions!$F$11-Contributions!E11</f>
         <v>3</v>
       </c>
@@ -1642,98 +2587,98 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27" style="3" customWidth="1"/>
-    <col min="2" max="2" width="26" style="3" customWidth="1"/>
-    <col min="3" max="3" width="46.33203125" customWidth="1"/>
+    <col min="1" max="1" width="33.77734375" style="21" customWidth="1"/>
+    <col min="2" max="2" width="39.88671875" style="21" customWidth="1"/>
+    <col min="3" max="3" width="56" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
+      <c r="A1" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="24">
         <v>1</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="6">
-        <v>1</v>
-      </c>
-      <c r="B4" s="8">
+      <c r="B4" s="26">
         <f>_xlfn.VAR.S(Contributions!B4:B11)</f>
         <v>4.2857142857142856</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="6">
-        <v>2</v>
-      </c>
-      <c r="B5" s="8">
+      <c r="A5" s="24">
+        <v>2</v>
+      </c>
+      <c r="B5" s="26">
         <f>_xlfn.VAR.S(Contributions!C4:C11)</f>
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="6">
+      <c r="A6" s="24">
         <v>3</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="26">
         <f>_xlfn.VAR.S(Contributions!D4:D11)</f>
         <v>1.0714285714285714</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="6">
-        <v>4</v>
-      </c>
-      <c r="B7" s="8">
+      <c r="A7" s="24">
+        <v>4</v>
+      </c>
+      <c r="B7" s="26">
         <f>_xlfn.VAR.S(Contributions!E4:E11)</f>
         <v>2.2142857142857144</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="B9" s="5">
+      <c r="A9" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="B9" s="23">
         <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="B10" s="8">
+      <c r="A10" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="B10" s="26">
         <f>SUM(B4:B7)</f>
         <v>13.571428571428569</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="B11" s="8">
+      <c r="A11" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="B11" s="26">
         <f>_xlfn.VAR.S(Contributions!F4:F11)</f>
         <v>22.285714285714285</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="B12" s="10">
+      <c r="A12" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12" s="28">
         <f>(B9/(B9-1))*(1-(B10/B11))</f>
         <v>0.5213675213675214</v>
       </c>
@@ -1745,139 +2690,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:D18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="24" style="3" customWidth="1"/>
-    <col min="2" max="2" width="14" style="3" customWidth="1"/>
-    <col min="3" max="3" width="5" style="3" customWidth="1"/>
-    <col min="4" max="4" width="47.44140625" style="3" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-    </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="6">
-        <v>1</v>
-      </c>
-      <c r="B5" s="8">
-        <f>Difficulte!E4</f>
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="6">
-        <v>2</v>
-      </c>
-      <c r="B6" s="8">
-        <f>Difficulte!E5</f>
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="6">
-        <v>3</v>
-      </c>
-      <c r="B7" s="8">
-        <f>Difficulte!E6</f>
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="6">
-        <v>4</v>
-      </c>
-      <c r="B8" s="8">
-        <f>Difficulte!E7</f>
-        <v>0.6875</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="6">
-        <v>1</v>
-      </c>
-      <c r="B12" s="8">
-        <f>Discrimination!D4</f>
-        <v>3.3058980245364314E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="6">
-        <v>2</v>
-      </c>
-      <c r="B13" s="8">
-        <f>Discrimination!D5</f>
-        <v>0.62994078834871203</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="6">
-        <v>3</v>
-      </c>
-      <c r="B14" s="8">
-        <f>Discrimination!D6</f>
-        <v>0.48434343544519759</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="6">
-        <v>4</v>
-      </c>
-      <c r="B15" s="8">
-        <f>Discrimination!D7</f>
-        <v>0.34879055774945689</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="B18" s="11">
-        <f>AlphaCronbach!B12</f>
-        <v>0.5213675213675214</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
 </file>